--- a/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
+++ b/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/myer056/GitHub/rc_sfa-rc-3-wenas-meta/agent_workflows/vibe_coding/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/jake_cavaiani_pnnl_gov/Documents/Documents/GitHub/rc_sfa-rc-3-wenas-meta/agent_workflows/vibe_coding/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E1BE90-A583-204A-ADB5-A1FAB842CF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{77E1BE90-A583-204A-ADB5-A1FAB842CF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDBD09F7-D57C-3A4D-B3B6-3D5B392B21BB}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="18780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10960" yWindow="-31240" windowWidth="68740" windowHeight="18780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="342">
   <si>
     <t>Watershed Pairing Review</t>
   </si>
@@ -193,9 +193,6 @@
     <t>pending_author_review</t>
   </si>
   <si>
-    <t>Shared reference and fire assignment require author review.</t>
-  </si>
-  <si>
     <t>Rhea_et_al_2021_C3</t>
   </si>
   <si>
@@ -313,9 +310,6 @@
     <t>one_to_one_candidate</t>
   </si>
   <si>
-    <t>Confirm which fire belongs to this comparison.</t>
-  </si>
-  <si>
     <t>Hickenbottom_et_al_2023_C2</t>
   </si>
   <si>
@@ -406,9 +400,6 @@
     <t>Coombs &amp; Melack; 2013 | Control_1_2_3</t>
   </si>
   <si>
-    <t>Multiple burned-watershed contrasts use the same reference identifier; confirm the study design and dependence handling.</t>
-  </si>
-  <si>
     <t>Coombs_Melack_2013_C2</t>
   </si>
   <si>
@@ -673,9 +664,6 @@
     <t>Burd et al 2018 | Control_1</t>
   </si>
   <si>
-    <t>Confirm that this is a study-designated burned-reference pair.</t>
-  </si>
-  <si>
     <t>Crandall_et_al_2021_C1</t>
   </si>
   <si>
@@ -901,13 +889,167 @@
     <t>needs_team_decision</t>
   </si>
   <si>
-    <t>AMP</t>
-  </si>
-  <si>
-    <t>Could not find PDF. Needs Jake to verify/supply pdf</t>
-  </si>
-  <si>
-    <t>study pdf downloaded</t>
+    <t>JSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of both fire perimeters. Red dots are the sampling locations (1 for the Rocky Fire, and 1 for the Wragg fire). The reference site is just beyond the Wragg fire and is used to compare between both burned sites. (Rocky, Wragg). Figure 2 shows the data. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This paper investigates 2 different wildfires each with 1 sampling site. Each burn is compared to the same reference site. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of the 2 wildfires that burned in 2012 (Hewlett and High Park Fire). Site PNF and PSF are both burned sites. PNF is within the Hewlett Fire and PSF is within the High Park burn perimeter. You might think that PNF is associated with the Hewlett fire and that PSF is associated with the High Park fire but the text says: "Onlya small area of the Hewlett Gulch Wildfire was upstream of thesampling locations, and thus potential effects on water qualityare primarily attributed to the High Park Wildfire". Should we just pull the burn characteristics for the High Park fire. Both burned sites are comparing to the reference PBR. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This paper investigates 2 burned sampling locations (PSF, PNF) and compares to the same reference site (PBR). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of both fire perimeters and sampling locations. Middle Fork is the burned site associated with the Mosquito Fire that is compared to the North Fork site (unbunred). Trout Creek is the burned watershed assoicated with the Caldor Fire that is compared to Cold Creek (Unburned). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This paper investigates 2 separate wildfires, each with a burned and unbunred 1:1 comparison. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 2 in the paper shows a map of the fire perimeter and the sampling sites. Coal Creek is the burned watershed associated with the Rampage Fire and compared to Pinchot Creek (Unburned).  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">We chose to only investigate Coal Creek (burned) compared to Pinchot Creek (unburned) that was associated with the Rampage Fire because it was a 1:1 comparison and control/reference study design. </t>
+  </si>
+  <si>
+    <t>There are multiple burned watersheds to a single reference site. This paper has 2 fires (High Park and Hayman Fire). B2 and B3 go to U3 (Hayman Fire). B1 go to U1 and U2 (High Park)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of the burned and unburned watersheds in the 2 different fires. The High Park Fire has B1 and compares it to U1 and U2. The Hayman Fire has B2 and B3 which are compared to U3. In the text, it looks like they are comparing burned vs. unburned and aggregating rather than 1:1. We should make sure the design makes sense and that we compare to the proper sites. </t>
+  </si>
+  <si>
+    <t>Figure 1 in the paper shows a map of the burned and unburned watersheds in the 2 different fires. The High Park Fire has B1 and compares it to U1 and U2. The Hayman Fire has B2 and B3 which are compared to U3.</t>
+  </si>
+  <si>
+    <t>Figure 1 in the paper shows a map of the Gaviota Fire perimeter and the 3 burned watersheds (San Onofre, Gaviota, and Arroyo Hondo). All of these sites are compared to the unburned site (Rattlesnake)</t>
+  </si>
+  <si>
+    <t>This study investigates 3 burned watersheds associated with the Gaviota Fire. All 3 watersheds (San Onofre, Gaviota, and Arroyo Hondo) are compared to one reference (Rattlesnake).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of the fire perimeter with all the sampling locations. Spanish Fork Lower (burned) is compared to Provo (unburned). Spanish Fork Upper (Burned) is compared to Provo (unburned). Benjamin Slough (Burned) is compared to Hobble Creek Lower (Unburned). Payson (Burned) is compared to Misubishi, Mill Race, and Dry Creek (Unburned) </t>
+  </si>
+  <si>
+    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of the burn perimeter and the sampling locations. East Fork Kootenai and Middle Fork Kootenai are the burned watersheds associated with the Matt fire and each are compared to the West Fork Kootenai. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study investigates 2 burned watersheds associated with the Matt Fire. Both watersheds ( East Fork and Middle Fork) are compared to a single reference (West Fork). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of the burn perimeter and the sampling locations. There are 3 burned watersheds (Akakola, Bowman, and Quartz) that are all associated with the Red Bench Fire. All 3 of these burned watersheds are compared to 1 reference site (Logging). Then the Red Bench Creek (Burned) is compared to Wally Creek (Unburned). Then there is Red Meadow Creek (Burned) which is compared to Coal Creek (Unburned). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study investigates 5 burned watersheds associated with the Red Bench Fire. Akakola, Bowman, and Quartz (burned) are compare to Logging Creek (Unburned). Red Bench Creek (burned) is compared with Wally Creek (unburned). And Red Meadow Creek (burned) is compared to Coal Creek (unburned). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of the burn perimeter and the sampling locations. There are 3 burned watersheds (DS1, DS2, and DS3) that are all associated with the Fourmile Canyon Fire. All 3 of these burned watersheds are compared to 1 reference site (US1). </t>
+  </si>
+  <si>
+    <t>This study investigates 3 burned watersheds associated with the Fourmile Canyon Fire. DS1, DS2, and DS3 (burned) all compare to US1 (Unburned).]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of the burn perimeter and the sampling locations. There are 3 burned watersheds (Site 2, Site 3, and Site 4) that are all associated with the Angora Fire. All 3 of these sites are compared to 1 reference site (Site 1). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study investigates 3 burned sites along Angora Creek that are associated with the Angora Fire. Site 1 was selected to represent the initial conditions of Angora Creek. Site 2 was within the burn area, Site 3 was located just below the burned area and site 4 was located downstream of the burn. We need to decide if they are "different" sites since they are all on the same creek. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of the burn perimeter and the sampling locations. There are 2 burned watersheds (PNF, PSF) that are both associated with the High Park Fire. Both of these sites are compared to 1 reference site (PBR). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study investigates 2 burned watersheds associated with the High Park Fire. Both burned watersheds (PNF, and PSF) compare to a single reference site (PBR). These are the same sites as from Writer et al. I think because Writer has both DOC and NO3 compared to this one that is just DOC, we should keep Writer and remove the redudancy of this paper.   </t>
+  </si>
+  <si>
+    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8). Mulitple reference sites to 1 burn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scotty Creek (SC) and Notawohka Creek (NW) drain catchments located in the discontinuous permafrost zone of Canada’s western boreal forest (Fig. 1). The SC outlet at the Liard Highway (61◦24 W, 121◦26 N) has a 134 km2 catchment that has not been affected by any major fires in the last 60 years. The NW outlet at the Mackenzie Highway (61◦08 W, 120◦17 N) has a 321 km2 catchment that was &gt;90 % burned in 2013. FIgure 4: Seasonal variation in catchment run-off and stream water chemistry measured at the outlets of Scotty Creek catchment and the
+recently burned Notawohka Creek catchment, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study investigates 1 burned watershed associated with the Northwest Territories fire that burned 90% of Notawohka Creek. Scotty Creek is the reference watershed. This study is located in Canada so I don’t think it is included because the lack of MTBS data. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study investigates 1 burned watershed associated with the Clovermist fire (Jones Creek). Jones Creek is compared to Crow Creek (unburned). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in the paper shows a map of the burn perimeter and the sampling locations. Jones Creek (burned) associated with the Clovermist fire is compared to Crow Creek (unburned). Figure 4 shows the comparison between the two watersheds. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1 in the paper lists the watersheds that were associated with the Jumping Branch Fire. Wash branch was the burned watershed that had no fertilization treatments that is compared to Crane Creek which is listed as the control watershed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1 in this paper has a time series of nitrate concentration of a burned watershed vs. an unburned watershed. Similarly to the Neary &amp; Currier paper, some watersheds has a fertilier treatment. We only used the sites that were not treated with fertilizer. Camas Creek (Burned) is compared to Grade Creek (reference). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study investigates 2 burned watersheds associated with the Safety Harbor Fire. Only Camas creek (Burned) and Grade Creek (Unburned) were used because they did not receive fertilizer treatment. We extracted data from Figure 1. This is an old paper and is before MTBS data so this paper would not be included in the final data frame due to the lack of MTBS data. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The PDF is in my Zotero. This study investigates 4 burned watersheds associated with the Jumping Branch Fire. Only Wash Branch was used becuse it did not receive a ferilization treatment like the other sites in this study. Wash Branch is compared to Crane Creek which is listed as the control watershed in Table 1. We extracted data from Figure 3. This is an old paper and is before MTBS data so this paper would not be included in the final data frame due to the lack of MTBS data. </t>
+  </si>
+  <si>
+    <t>Hayman_Fire_2002</t>
+  </si>
+  <si>
+    <t>Rocky_Fire_2015</t>
+  </si>
+  <si>
+    <t>Wragg_Fire_2015</t>
+  </si>
+  <si>
+    <t>Hewlett_Gulch_2012</t>
+  </si>
+  <si>
+    <t>High_Park_Fire_2012</t>
+  </si>
+  <si>
+    <t>Caldor_Fire_2021</t>
+  </si>
+  <si>
+    <t>Mosquito_Fire_2022</t>
+  </si>
+  <si>
+    <t>Rampage_Fire_2003</t>
+  </si>
+  <si>
+    <t>Gaviota_Fire_2004</t>
+  </si>
+  <si>
+    <t>Pole_Creek_Fire_Complex_2018</t>
+  </si>
+  <si>
+    <t>Matt_Fire_1985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red_Bench_Fire_1988 </t>
+  </si>
+  <si>
+    <t>Fourmile_Canyon_Fire_2010</t>
+  </si>
+  <si>
+    <t>Angora_Fire_2007</t>
+  </si>
+  <si>
+    <t>Northwest_Territories_Fire_2013</t>
+  </si>
+  <si>
+    <t>Clover_Mist_Wildfire_1988</t>
+  </si>
+  <si>
+    <t>Jumping_Branch_Wildfire_1978</t>
+  </si>
+  <si>
+    <t>Safety_Harbor_Fire_1970</t>
+  </si>
+  <si>
+    <t>There are multiple burned watersheds to a single reference site. This paper has 2 fires (High Park and Hayman Fire). B2 and B3 go to U3 (Hayman Fire). B1 go to U1 and U2 (High Park). U3 is designated as Control_2_3 because it is used to compare between Site 2 (B2) and Site 3 (B3)</t>
   </si>
 </sst>
 </file>
@@ -917,7 +1059,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -951,8 +1093,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -966,17 +1114,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1007,26 +1174,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1409,10 +1594,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="4"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1500,7 +1685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
@@ -1518,7 +1703,7 @@
     <col min="29" max="29" width="55.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -1607,190 +1792,220 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:32" s="6" customFormat="1" ht="80" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="10">
         <v>2017</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="10">
         <v>2017</v>
       </c>
-      <c r="O2" s="1">
-        <v>1</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="10">
+        <v>1</v>
+      </c>
+      <c r="P2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="10">
         <v>2</v>
       </c>
-      <c r="R2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="T2" s="1" t="s">
+      <c r="R2" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="2" t="s">
+      <c r="V2" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X2" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB2" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+    </row>
+    <row r="3" spans="1:32" s="6" customFormat="1" ht="80" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="D3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="11">
+        <v>2017</v>
+      </c>
+      <c r="N3" s="11">
+        <v>2017</v>
+      </c>
+      <c r="O3" s="11">
+        <v>1</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>2</v>
+      </c>
+      <c r="R3" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="W3" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X3" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z3" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB3" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+    </row>
+    <row r="4" spans="1:32" ht="112" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="1">
-        <v>2017</v>
-      </c>
-      <c r="N3" s="1">
-        <v>2017</v>
-      </c>
-      <c r="O3" s="1">
-        <v>1</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>2</v>
-      </c>
-      <c r="R3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" ht="64" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>50</v>
@@ -1808,7 +2023,7 @@
         <v>2</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q4" s="1">
         <v>2</v>
@@ -1825,49 +2040,61 @@
       <c r="U4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" ht="64" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="V4" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC4" s="7" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="112" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="I5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>50</v>
@@ -1885,7 +2112,7 @@
         <v>2</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q5" s="1">
         <v>2</v>
@@ -1902,49 +2129,61 @@
       <c r="U5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="V5" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z5" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB5" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC5" s="7" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="256" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>50</v>
@@ -1962,7 +2201,7 @@
         <v>2</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="1">
         <v>2</v>
@@ -1979,49 +2218,61 @@
       <c r="U6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="V6" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X6" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z6" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA6" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC6" s="7" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="256" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="I7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>50</v>
@@ -2039,7 +2290,7 @@
         <v>2</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="1">
         <v>2</v>
@@ -2056,49 +2307,61 @@
       <c r="U7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="V7" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="W7" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X7" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z7" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA7" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB7" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC7" s="7" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="128" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>50</v>
@@ -2116,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q8" s="1">
         <v>1</v>
@@ -2131,51 +2394,63 @@
         <v>53</v>
       </c>
       <c r="U8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="X8" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z8" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA8" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB8" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC8" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="128" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="I9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>50</v>
@@ -2193,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="1">
         <v>1</v>
@@ -2208,51 +2483,63 @@
         <v>53</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="X9" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z9" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB9" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC9" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="80" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>50</v>
@@ -2270,7 +2557,7 @@
         <v>4</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q10" s="1">
         <v>1</v>
@@ -2285,45 +2572,57 @@
         <v>53</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
+      </c>
+      <c r="V10" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="W10" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="X10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA10" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB10" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC10" s="7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="160" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>48</v>
@@ -2347,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q11" s="1">
         <v>1</v>
@@ -2362,57 +2661,69 @@
         <v>53</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V11" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="W11" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="X11" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z11" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="AA11" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC11" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" ht="80" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M12" s="1">
         <v>2004</v>
@@ -2424,7 +2735,7 @@
         <v>2</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q12" s="1">
         <v>3</v>
@@ -2441,55 +2752,67 @@
       <c r="U12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>116</v>
+      <c r="V12" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="W12" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X12" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z12" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA12" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB12" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC12" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="80" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="J13" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M13" s="1">
         <v>2004</v>
@@ -2501,7 +2824,7 @@
         <v>2</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q13" s="1">
         <v>3</v>
@@ -2518,55 +2841,67 @@
       <c r="U13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>116</v>
+      <c r="V13" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X13" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z13" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA13" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC13" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="80" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="J14" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M14" s="1">
         <v>2004</v>
@@ -2578,7 +2913,7 @@
         <v>2</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q14" s="1">
         <v>3</v>
@@ -2595,49 +2930,61 @@
       <c r="U14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>116</v>
+      <c r="V14" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="W14" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X14" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z14" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA14" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB14" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC14" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="144" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>50</v>
@@ -2655,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q15" s="1">
         <v>2</v>
@@ -2672,49 +3019,61 @@
       <c r="U15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>116</v>
+      <c r="V15" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="W15" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X15" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z15" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA15" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB15" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC15" s="7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="144" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="G16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>50</v>
@@ -2732,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q16" s="1">
         <v>2</v>
@@ -2749,55 +3108,67 @@
       <c r="U16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>116</v>
+      <c r="V16" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="W16" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X16" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z16" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA16" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB16" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC16" s="7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M17" s="1">
         <v>1985</v>
@@ -2809,7 +3180,7 @@
         <v>4</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q17" s="1">
         <v>2</v>
@@ -2826,55 +3197,67 @@
       <c r="U17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>116</v>
+      <c r="V17" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X17" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z17" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="AA17" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB17" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC17" s="7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M18" s="1">
         <v>1985</v>
@@ -2886,7 +3269,7 @@
         <v>4</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q18" s="1">
         <v>2</v>
@@ -2903,55 +3286,67 @@
       <c r="U18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>116</v>
+      <c r="V18" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="W18" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X18" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z18" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="AA18" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB18" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC18" s="7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="160" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M19" s="1">
         <v>1989</v>
@@ -2963,7 +3358,7 @@
         <v>4</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Q19" s="1">
         <v>3</v>
@@ -2980,55 +3375,67 @@
       <c r="U19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>116</v>
+      <c r="V19" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="W19" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X19" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z19" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA19" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB19" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC19" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="160" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M20" s="1">
         <v>1991</v>
@@ -3040,7 +3447,7 @@
         <v>2</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Q20" s="1">
         <v>3</v>
@@ -3057,55 +3464,67 @@
       <c r="U20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="3"/>
-      <c r="AC20" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" ht="48" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>116</v>
+      <c r="V20" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="W20" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X20" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z20" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA20" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB20" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC20" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="160" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="G21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M21" s="1">
         <v>1989</v>
@@ -3117,7 +3536,7 @@
         <v>3</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Q21" s="1">
         <v>3</v>
@@ -3134,49 +3553,61 @@
       <c r="U21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="3"/>
-      <c r="AC21" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>116</v>
+      <c r="V21" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="W21" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X21" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z21" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA21" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB21" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC21" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>50</v>
@@ -3194,7 +3625,7 @@
         <v>5</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q22" s="1">
         <v>3</v>
@@ -3211,49 +3642,61 @@
       <c r="U22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="3"/>
-      <c r="AC22" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>116</v>
+      <c r="V22" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="W22" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X22" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z22" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA22" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB22" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC22" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>50</v>
@@ -3271,7 +3714,7 @@
         <v>5</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q23" s="1">
         <v>3</v>
@@ -3288,49 +3731,61 @@
       <c r="U23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
-      <c r="AB23" s="3"/>
-      <c r="AC23" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>116</v>
+      <c r="V23" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="W23" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X23" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z23" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA23" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB23" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC23" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>50</v>
@@ -3348,7 +3803,7 @@
         <v>5</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q24" s="1">
         <v>3</v>
@@ -3365,55 +3820,67 @@
       <c r="U24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="3"/>
-      <c r="AC24" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>116</v>
+      <c r="V24" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="W24" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X24" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z24" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA24" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC24" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M25" s="1">
         <v>2008</v>
@@ -3425,7 +3892,7 @@
         <v>2</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q25" s="1">
         <v>3</v>
@@ -3442,55 +3909,67 @@
       <c r="U25" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
-      <c r="AB25" s="3"/>
-      <c r="AC25" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>116</v>
+      <c r="V25" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="W25" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X25" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z25" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB25" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC25" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M26" s="1">
         <v>2008</v>
@@ -3502,7 +3981,7 @@
         <v>2</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q26" s="1">
         <v>3</v>
@@ -3519,55 +3998,67 @@
       <c r="U26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z26" s="2"/>
-      <c r="AA26" s="2"/>
-      <c r="AB26" s="3"/>
-      <c r="AC26" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>116</v>
+      <c r="V26" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="W26" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X26" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z26" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="AA26" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB26" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC26" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="J27" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M27" s="1">
         <v>2008</v>
@@ -3579,7 +4070,7 @@
         <v>2</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q27" s="1">
         <v>3</v>
@@ -3596,55 +4087,67 @@
       <c r="U27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
-      <c r="Y27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z27" s="2"/>
-      <c r="AA27" s="2"/>
-      <c r="AB27" s="3"/>
-      <c r="AC27" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>116</v>
+      <c r="V27" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="W27" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X27" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z27" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="AA27" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC27" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M28" s="1">
         <v>2013</v>
@@ -3656,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q28" s="1">
         <v>2</v>
@@ -3673,55 +4176,67 @@
       <c r="U28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
-      <c r="Y28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z28" s="2"/>
-      <c r="AA28" s="2"/>
-      <c r="AB28" s="3"/>
-      <c r="AC28" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>116</v>
+      <c r="V28" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="W28" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X28" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z28" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA28" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC28" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="H29" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M29" s="1">
         <v>2013</v>
@@ -3733,7 +4248,7 @@
         <v>1</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q29" s="1">
         <v>2</v>
@@ -3750,55 +4265,67 @@
       <c r="U29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
-      <c r="Y29" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z29" s="2"/>
-      <c r="AA29" s="2"/>
-      <c r="AB29" s="3"/>
-      <c r="AC29" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" ht="32" x14ac:dyDescent="0.2">
+      <c r="V29" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="W29" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X29" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z29" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA29" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB29" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC29" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="256" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="F30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M30" s="1">
         <v>2016</v>
@@ -3810,7 +4337,7 @@
         <v>1</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q30" s="1">
         <v>1</v>
@@ -3825,55 +4352,63 @@
         <v>53</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
-      <c r="Y30" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z30" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA30" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB30" s="3"/>
-      <c r="AC30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V30" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="W30" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="X30" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z30" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="AA30" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB30" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC30" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="144" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="31" spans="1:29" ht="32" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="I31" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>50</v>
@@ -3891,7 +4426,7 @@
         <v>1</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Q31" s="1">
         <v>1</v>
@@ -3906,55 +4441,63 @@
         <v>53</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V31" s="2"/>
-      <c r="W31" s="2"/>
-      <c r="X31" s="2"/>
-      <c r="Y31" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z31" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA31" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB31" s="3"/>
-      <c r="AC31" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" ht="32" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+      <c r="V31" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="W31" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X31" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z31" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA31" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB31" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC31" s="7" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" ht="144" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>50</v>
@@ -3972,7 +4515,7 @@
         <v>1</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="Q32" s="1">
         <v>1</v>
@@ -3987,61 +4530,69 @@
         <v>53</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-      <c r="Y32" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z32" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA32" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB32" s="3"/>
-      <c r="AC32" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29" ht="32" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+      <c r="V32" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="W32" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X32" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z32" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA32" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB32" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC32" s="7" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" ht="96" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="J33" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M33" s="1">
         <v>1989</v>
@@ -4053,7 +4604,7 @@
         <v>5</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Q33" s="1">
         <v>1</v>
@@ -4068,61 +4619,69 @@
         <v>53</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V33" s="2"/>
-      <c r="W33" s="2"/>
-      <c r="X33" s="2"/>
-      <c r="Y33" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z33" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA33" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB33" s="3"/>
-      <c r="AC33" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" ht="32" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+      <c r="V33" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="W33" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="X33" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z33" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="AA33" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB33" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC33" s="7" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M34" s="1">
         <v>1989</v>
@@ -4134,7 +4693,7 @@
         <v>3</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="Q34" s="1">
         <v>1</v>
@@ -4149,61 +4708,69 @@
         <v>53</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V34" s="2"/>
-      <c r="W34" s="2"/>
-      <c r="X34" s="2"/>
-      <c r="Y34" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z34" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA34" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB34" s="3"/>
-      <c r="AC34" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29" ht="32" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+      <c r="V34" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="W34" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X34" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z34" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA34" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC34" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M35" s="1">
         <v>1989</v>
@@ -4215,7 +4782,7 @@
         <v>3</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="Q35" s="1">
         <v>1</v>
@@ -4230,61 +4797,69 @@
         <v>53</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V35" s="2"/>
-      <c r="W35" s="2"/>
-      <c r="X35" s="2"/>
-      <c r="Y35" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z35" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA35" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB35" s="3"/>
-      <c r="AC35" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29" ht="32" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+      <c r="V35" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="W35" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="X35" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z35" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA35" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB35" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC35" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" ht="112" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M36" s="1">
         <v>1978</v>
@@ -4296,7 +4871,7 @@
         <v>2</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Q36" s="1">
         <v>1</v>
@@ -4311,59 +4886,69 @@
         <v>53</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V36" s="2"/>
-      <c r="W36" s="2"/>
-      <c r="X36" s="2"/>
-      <c r="Y36" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z36" s="2"/>
-      <c r="AA36" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB36" s="3"/>
-      <c r="AC36" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29" ht="32" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+      <c r="V36" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="W36" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="X36" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z36" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="AA36" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC36" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" ht="128" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M37" s="1">
         <v>1970</v>
@@ -4375,7 +4960,7 @@
         <v>3</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Q37" s="1">
         <v>1</v>
@@ -4390,23 +4975,31 @@
         <v>53</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V37" s="2"/>
-      <c r="W37" s="2"/>
-      <c r="X37" s="2"/>
-      <c r="Y37" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z37" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA37" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB37" s="3"/>
-      <c r="AC37" s="2" t="s">
-        <v>216</v>
+        <v>94</v>
+      </c>
+      <c r="V37" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="W37" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="X37" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z37" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="AA37" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB37" s="8">
+        <v>46265</v>
+      </c>
+      <c r="AC37" s="7" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -4455,10 +5048,10 @@
         <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F1" t="s">
         <v>29</v>
@@ -4467,10 +5060,10 @@
         <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -4496,21 +5089,21 @@
         <v>51</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="80" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -4525,21 +5118,21 @@
         <v>51</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -4554,21 +5147,21 @@
         <v>51</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -4583,21 +5176,21 @@
         <v>51</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -4612,21 +5205,21 @@
         <v>51</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -4638,24 +5231,24 @@
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D8" s="1">
         <v>5</v>
@@ -4667,24 +5260,24 @@
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -4699,21 +5292,21 @@
         <v>51</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -4725,24 +5318,24 @@
         <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -4757,21 +5350,21 @@
         <v>51</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -4783,24 +5376,24 @@
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
@@ -4812,24 +5405,24 @@
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -4841,24 +5434,24 @@
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -4870,24 +5463,24 @@
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -4899,24 +5492,24 @@
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -4928,13 +5521,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4957,10 +5550,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -4968,7 +5561,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -4976,7 +5569,7 @@
         <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -4984,7 +5577,7 @@
         <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4992,7 +5585,7 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -5000,7 +5593,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -5008,7 +5601,7 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -5016,7 +5609,7 @@
         <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -5024,7 +5617,7 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -5040,7 +5633,7 @@
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -5048,7 +5641,7 @@
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -5056,7 +5649,7 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -5064,7 +5657,7 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
